--- a/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
+++ b/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="26827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\accesibilidad\normas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1ED71EC-08D4-421C-905E-C1DFB19457E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D592E1A2-E57B-4847-8BF8-585C53F00A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{974282F1-0557-4C69-836B-12F6339D2A22}"/>
   </bookViews>
@@ -371,7 +371,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="767" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="253">
   <si>
     <t>5.2 Activación de características de accesibilidad</t>
   </si>
@@ -1132,6 +1132,9 @@
   </si>
   <si>
     <t>Dispositivo móvil</t>
+  </si>
+  <si>
+    <t>Convertidor de documento a txt</t>
   </si>
 </sst>
 </file>
@@ -7172,7 +7175,9 @@
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
       <c r="L97" s="8"/>
-      <c r="M97" s="5"/>
+      <c r="M97" s="5" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="98" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A98" s="13">

--- a/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
+++ b/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\accesibilidad\normas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoseR\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D592E1A2-E57B-4847-8BF8-585C53F00A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20D07DE-C9D5-4F0A-93CE-2929A5303899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{974282F1-0557-4C69-836B-12F6339D2A22}"/>
   </bookViews>
@@ -371,7 +371,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="768" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="253">
   <si>
     <t>5.2 Activación de características de accesibilidad</t>
   </si>
@@ -2957,7 +2957,9 @@
       </c>
       <c r="C65" s="5"/>
       <c r="D65" s="8"/>
-      <c r="E65" s="6"/>
+      <c r="E65" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="F65" s="5"/>
       <c r="G65" s="8" t="s">
         <v>141</v>
@@ -3001,7 +3003,9 @@
       </c>
       <c r="C67" s="5"/>
       <c r="D67" s="8"/>
-      <c r="E67" s="5"/>
+      <c r="E67" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="F67" s="5"/>
       <c r="G67" s="8" t="s">
         <v>141</v>
@@ -3101,7 +3105,9 @@
       </c>
       <c r="C72" s="5"/>
       <c r="D72" s="8"/>
-      <c r="E72" s="6"/>
+      <c r="E72" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="F72" s="5"/>
       <c r="G72" s="8" t="s">
         <v>141</v>
@@ -4057,7 +4063,9 @@
       <c r="B119" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="C119" s="5"/>
+      <c r="C119" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="D119" s="8"/>
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
@@ -4157,7 +4165,9 @@
       <c r="B124" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C124" s="5"/>
+      <c r="C124" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="D124" s="8"/>
       <c r="E124" s="6"/>
       <c r="F124" s="5"/>
@@ -5024,6 +5034,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5114,7 +5125,7 @@
       </c>
       <c r="M2" s="5"/>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -5135,7 +5146,7 @@
       </c>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -5156,7 +5167,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="5"/>
     </row>
-    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -5177,7 +5188,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -5198,7 +5209,7 @@
       </c>
       <c r="M6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -5219,7 +5230,7 @@
       <c r="L7" s="8"/>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -5240,7 +5251,7 @@
       <c r="L8" s="8"/>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -5263,7 +5274,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -5284,7 +5295,7 @@
       <c r="L10" s="8"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -5305,7 +5316,7 @@
       <c r="L11" s="8"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -5326,7 +5337,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -5347,7 +5358,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -5368,7 +5379,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -5389,7 +5400,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -5412,7 +5423,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -5433,7 +5444,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -5454,7 +5465,7 @@
       </c>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>18</v>
       </c>
@@ -5475,7 +5486,7 @@
       <c r="L19" s="8"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -5496,7 +5507,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>20</v>
       </c>
@@ -5517,7 +5528,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>21</v>
       </c>
@@ -5538,7 +5549,7 @@
       </c>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -5559,7 +5570,7 @@
       </c>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -5580,7 +5591,7 @@
       </c>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
         <v>24</v>
       </c>
@@ -5603,7 +5614,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -5624,7 +5635,7 @@
       <c r="L26" s="8"/>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <v>26</v>
       </c>
@@ -5645,7 +5656,7 @@
       <c r="L27" s="8"/>
       <c r="M27" s="6"/>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -5666,7 +5677,7 @@
       <c r="L28" s="8"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -5687,7 +5698,7 @@
       </c>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -5708,7 +5719,7 @@
       </c>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -5729,7 +5740,7 @@
       <c r="L31" s="8"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -5775,7 +5786,7 @@
       <c r="L33" s="8"/>
       <c r="M33" s="5"/>
     </row>
-    <row r="34" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -5796,7 +5807,7 @@
       <c r="L34" s="8"/>
       <c r="M34" s="5"/>
     </row>
-    <row r="35" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -5817,7 +5828,7 @@
       </c>
       <c r="M35" s="5"/>
     </row>
-    <row r="36" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -5838,7 +5849,7 @@
       <c r="L36" s="8"/>
       <c r="M36" s="5"/>
     </row>
-    <row r="37" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -5886,7 +5897,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="5"/>
     </row>
-    <row r="39" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -5907,7 +5918,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="5"/>
     </row>
-    <row r="40" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -5928,7 +5939,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -5949,7 +5960,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>41</v>
       </c>
@@ -5970,7 +5981,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -5986,10 +5997,12 @@
       <c r="I43" s="5"/>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
-      <c r="L43" s="9"/>
+      <c r="L43" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="M43" s="5"/>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -6035,7 +6048,7 @@
       <c r="L45" s="8"/>
       <c r="M45" s="5"/>
     </row>
-    <row r="46" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -6056,7 +6069,7 @@
       <c r="L46" s="8"/>
       <c r="M46" s="6"/>
     </row>
-    <row r="47" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -6077,7 +6090,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="5"/>
     </row>
-    <row r="48" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -6123,7 +6136,7 @@
       <c r="L49" s="8"/>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -6144,7 +6157,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
         <v>50</v>
       </c>
@@ -6167,7 +6180,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="13">
         <v>51</v>
       </c>
@@ -6190,7 +6203,7 @@
       <c r="L52" s="8"/>
       <c r="M52" s="5"/>
     </row>
-    <row r="53" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="13">
         <v>52</v>
       </c>
@@ -6213,7 +6226,7 @@
       <c r="L53" s="8"/>
       <c r="M53" s="5"/>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="13">
         <v>53</v>
       </c>
@@ -6236,7 +6249,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="5"/>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="13">
         <v>54</v>
       </c>
@@ -6257,7 +6270,7 @@
       </c>
       <c r="M55" s="6"/>
     </row>
-    <row r="56" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="13">
         <v>55</v>
       </c>
@@ -6273,12 +6286,14 @@
       <c r="I56" s="5"/>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
-      <c r="L56" s="8"/>
+      <c r="L56" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="M56" s="6" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="66" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="66" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="13">
         <v>56</v>
       </c>
@@ -6299,7 +6314,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="13">
         <v>57</v>
       </c>
@@ -6327,7 +6342,9 @@
       <c r="B59" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="5"/>
+      <c r="C59" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="D59" s="8"/>
       <c r="E59" s="6"/>
       <c r="F59" s="5"/>
@@ -6343,7 +6360,7 @@
       </c>
       <c r="M59" s="6"/>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="13">
         <v>59</v>
       </c>
@@ -6373,7 +6390,9 @@
       <c r="B61" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="C61" s="5"/>
+      <c r="C61" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="D61" s="8"/>
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
@@ -6389,7 +6408,7 @@
       <c r="L61" s="8"/>
       <c r="M61" s="5"/>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="13">
         <v>61</v>
       </c>
@@ -6410,7 +6429,7 @@
       </c>
       <c r="M62" s="5"/>
     </row>
-    <row r="63" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="13">
         <v>62</v>
       </c>
@@ -6431,7 +6450,7 @@
       </c>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="13">
         <v>63</v>
       </c>
@@ -6452,7 +6471,7 @@
       <c r="L64" s="8"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="13">
         <v>64</v>
       </c>
@@ -6473,7 +6492,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="13">
         <v>65</v>
       </c>
@@ -6501,7 +6520,9 @@
       <c r="B67" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C67" s="5"/>
+      <c r="C67" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="D67" s="8"/>
       <c r="E67" s="6"/>
       <c r="F67" s="5"/>
@@ -6519,7 +6540,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -6590,7 +6611,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -6611,7 +6632,7 @@
       <c r="L71" s="8"/>
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="13">
         <v>71</v>
       </c>
@@ -6641,7 +6662,9 @@
       <c r="B73" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="C73" s="6"/>
+      <c r="C73" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="D73" s="8"/>
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
@@ -6682,7 +6705,7 @@
       </c>
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="13">
         <v>74</v>
       </c>
@@ -6703,7 +6726,7 @@
       <c r="L75" s="8"/>
       <c r="M75" s="6"/>
     </row>
-    <row r="76" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="13">
         <v>75</v>
       </c>
@@ -6724,7 +6747,7 @@
       </c>
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="13">
         <v>76</v>
       </c>
@@ -6745,7 +6768,7 @@
       <c r="L77" s="8"/>
       <c r="M77" s="6"/>
     </row>
-    <row r="78" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="13">
         <v>77</v>
       </c>
@@ -6812,7 +6835,7 @@
       <c r="L80" s="8"/>
       <c r="M80" s="5"/>
     </row>
-    <row r="81" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="13">
         <v>80</v>
       </c>
@@ -6833,7 +6856,7 @@
       <c r="L81" s="8"/>
       <c r="M81" s="5"/>
     </row>
-    <row r="82" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="13">
         <v>81</v>
       </c>
@@ -6854,7 +6877,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="13">
         <v>82</v>
       </c>
@@ -6877,7 +6900,7 @@
       <c r="L83" s="8"/>
       <c r="M83" s="5"/>
     </row>
-    <row r="84" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="13">
         <v>83</v>
       </c>
@@ -6898,7 +6921,7 @@
       <c r="L84" s="8"/>
       <c r="M84" s="5"/>
     </row>
-    <row r="85" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="13">
         <v>84</v>
       </c>
@@ -6919,7 +6942,7 @@
       </c>
       <c r="M85" s="5"/>
     </row>
-    <row r="86" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="13">
         <v>85</v>
       </c>
@@ -6940,7 +6963,7 @@
       <c r="L86" s="8"/>
       <c r="M86" s="5"/>
     </row>
-    <row r="87" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="13">
         <v>86</v>
       </c>
@@ -6963,7 +6986,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="13">
         <v>87</v>
       </c>
@@ -6986,7 +7009,7 @@
       <c r="L88" s="8"/>
       <c r="M88" s="5"/>
     </row>
-    <row r="89" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="13">
         <v>88</v>
       </c>
@@ -7007,7 +7030,7 @@
       <c r="L89" s="8"/>
       <c r="M89" s="5"/>
     </row>
-    <row r="90" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="13">
         <v>89</v>
       </c>
@@ -7028,7 +7051,7 @@
       <c r="L90" s="8"/>
       <c r="M90" s="5"/>
     </row>
-    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="13">
         <v>90</v>
       </c>
@@ -7049,7 +7072,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="13">
         <v>91</v>
       </c>
@@ -7070,7 +7093,7 @@
       <c r="L92" s="8"/>
       <c r="M92" s="5"/>
     </row>
-    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="13">
         <v>92</v>
       </c>
@@ -7089,7 +7112,7 @@
       <c r="L93" s="9"/>
       <c r="M93" s="5"/>
     </row>
-    <row r="94" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="13">
         <v>93</v>
       </c>
@@ -7112,7 +7135,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="13">
         <v>94</v>
       </c>
@@ -7135,7 +7158,7 @@
       <c r="L95" s="8"/>
       <c r="M95" s="5"/>
     </row>
-    <row r="96" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="13">
         <v>95</v>
       </c>
@@ -7156,7 +7179,7 @@
       <c r="L96" s="8"/>
       <c r="M96" s="6"/>
     </row>
-    <row r="97" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="13">
         <v>96</v>
       </c>
@@ -7179,7 +7202,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="13">
         <v>97</v>
       </c>
@@ -7200,7 +7223,7 @@
       <c r="L98" s="8"/>
       <c r="M98" s="5"/>
     </row>
-    <row r="99" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="13">
         <v>98</v>
       </c>
@@ -7223,7 +7246,7 @@
       <c r="L99" s="8"/>
       <c r="M99" s="5"/>
     </row>
-    <row r="100" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="13">
         <v>99</v>
       </c>
@@ -7244,7 +7267,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="13">
         <v>100</v>
       </c>
@@ -7267,7 +7290,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="13">
         <v>101</v>
       </c>
@@ -7290,7 +7313,7 @@
       <c r="L102" s="8"/>
       <c r="M102" s="5"/>
     </row>
-    <row r="103" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="13">
         <v>102</v>
       </c>
@@ -7313,7 +7336,7 @@
       <c r="L103" s="8"/>
       <c r="M103" s="5"/>
     </row>
-    <row r="104" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="13">
         <v>103</v>
       </c>
@@ -7336,7 +7359,7 @@
       <c r="L104" s="8"/>
       <c r="M104" s="5"/>
     </row>
-    <row r="105" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="13">
         <v>104</v>
       </c>
@@ -7357,7 +7380,7 @@
       </c>
       <c r="M105" s="6"/>
     </row>
-    <row r="106" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="13">
         <v>105</v>
       </c>
@@ -7378,7 +7401,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="66" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="66" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="13">
         <v>106</v>
       </c>
@@ -7399,7 +7422,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="13">
         <v>107</v>
       </c>
@@ -7408,7 +7431,9 @@
       </c>
       <c r="C108" s="5"/>
       <c r="D108" s="8"/>
-      <c r="E108" s="6"/>
+      <c r="E108" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="F108" s="5"/>
       <c r="G108" s="8" t="s">
         <v>141</v>
@@ -7422,7 +7447,7 @@
       </c>
       <c r="M108" s="6"/>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="13">
         <v>108</v>
       </c>
@@ -7445,7 +7470,7 @@
       <c r="L109" s="8"/>
       <c r="M109" s="5"/>
     </row>
-    <row r="110" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="13">
         <v>109</v>
       </c>
@@ -7454,7 +7479,9 @@
       </c>
       <c r="C110" s="5"/>
       <c r="D110" s="8"/>
-      <c r="E110" s="5"/>
+      <c r="E110" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="F110" s="5"/>
       <c r="G110" s="8" t="s">
         <v>141</v>
@@ -7468,7 +7495,7 @@
       <c r="L110" s="8"/>
       <c r="M110" s="5"/>
     </row>
-    <row r="111" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="13">
         <v>110</v>
       </c>
@@ -7489,7 +7516,7 @@
       <c r="L111" s="8"/>
       <c r="M111" s="5"/>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="13">
         <v>111</v>
       </c>
@@ -7510,7 +7537,7 @@
       <c r="L112" s="8"/>
       <c r="M112" s="5"/>
     </row>
-    <row r="113" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="13">
         <v>112</v>
       </c>
@@ -7531,7 +7558,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="13">
         <v>113</v>
       </c>
@@ -7552,7 +7579,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="13">
         <v>114</v>
       </c>
@@ -7561,7 +7588,9 @@
       </c>
       <c r="C115" s="5"/>
       <c r="D115" s="8"/>
-      <c r="E115" s="6"/>
+      <c r="E115" s="6" t="s">
+        <v>141</v>
+      </c>
       <c r="F115" s="5"/>
       <c r="G115" s="8" t="s">
         <v>141</v>
@@ -7577,7 +7606,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="13">
         <v>115</v>
       </c>
@@ -7598,7 +7627,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="13">
         <v>116</v>
       </c>
@@ -7621,7 +7650,7 @@
       <c r="L117" s="8"/>
       <c r="M117" s="5"/>
     </row>
-    <row r="118" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="13">
         <v>117</v>
       </c>
@@ -7644,7 +7673,7 @@
       <c r="L118" s="8"/>
       <c r="M118" s="5"/>
     </row>
-    <row r="119" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="13">
         <v>118</v>
       </c>
@@ -7665,7 +7694,7 @@
       <c r="L119" s="8"/>
       <c r="M119" s="5"/>
     </row>
-    <row r="120" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13">
         <v>119</v>
       </c>
@@ -7688,7 +7717,7 @@
       <c r="L120" s="8"/>
       <c r="M120" s="5"/>
     </row>
-    <row r="121" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="13">
         <v>120</v>
       </c>
@@ -7709,7 +7738,7 @@
       <c r="L121" s="8"/>
       <c r="M121" s="6"/>
     </row>
-    <row r="122" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="13">
         <v>121</v>
       </c>
@@ -7730,7 +7759,7 @@
       </c>
       <c r="M122" s="5"/>
     </row>
-    <row r="123" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="13">
         <v>122</v>
       </c>
@@ -7751,7 +7780,7 @@
       <c r="L123" s="8"/>
       <c r="M123" s="6"/>
     </row>
-    <row r="124" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="13">
         <v>123</v>
       </c>
@@ -7772,7 +7801,7 @@
       <c r="L124" s="8"/>
       <c r="M124" s="5"/>
     </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="13">
         <v>124</v>
       </c>
@@ -7793,7 +7822,7 @@
       <c r="L125" s="8"/>
       <c r="M125" s="5"/>
     </row>
-    <row r="126" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="13">
         <v>125</v>
       </c>
@@ -7816,7 +7845,7 @@
       <c r="L126" s="8"/>
       <c r="M126" s="5"/>
     </row>
-    <row r="127" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="13">
         <v>126</v>
       </c>
@@ -7837,7 +7866,7 @@
       <c r="L127" s="8"/>
       <c r="M127" s="5"/>
     </row>
-    <row r="128" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="13">
         <v>127</v>
       </c>
@@ -7858,7 +7887,7 @@
       <c r="L128" s="8"/>
       <c r="M128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="13">
         <v>128</v>
       </c>
@@ -7879,7 +7908,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="13">
         <v>129</v>
       </c>
@@ -7900,7 +7929,7 @@
       </c>
       <c r="M130" s="5"/>
     </row>
-    <row r="131" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="13">
         <v>130</v>
       </c>
@@ -7923,7 +7952,7 @@
       <c r="L131" s="8"/>
       <c r="M131" s="5"/>
     </row>
-    <row r="132" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="13">
         <v>131</v>
       </c>
@@ -7944,7 +7973,7 @@
       </c>
       <c r="M132" s="5"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="13">
         <v>132</v>
       </c>
@@ -7965,7 +7994,7 @@
       </c>
       <c r="M133" s="5"/>
     </row>
-    <row r="134" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="13">
         <v>133</v>
       </c>
@@ -8025,7 +8054,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="13">
         <v>135</v>
       </c>
@@ -8121,7 +8150,13 @@
       <c r="M138" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M138" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
+  <autoFilter ref="A1:M138" xr:uid="{00000000-0001-0000-0400-000000000000}">
+    <filterColumn colId="2">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
+++ b/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JoseR\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\accesibilidad\normas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20D07DE-C9D5-4F0A-93CE-2929A5303899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8273440-59F9-473C-9828-84E7599CD3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{974282F1-0557-4C69-836B-12F6339D2A22}"/>
   </bookViews>
@@ -5034,7 +5034,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5125,7 +5124,7 @@
       </c>
       <c r="M2" s="5"/>
     </row>
-    <row r="3" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="13">
         <v>2</v>
       </c>
@@ -5146,7 +5145,7 @@
       </c>
       <c r="M3" s="5"/>
     </row>
-    <row r="4" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A4" s="13">
         <v>3</v>
       </c>
@@ -5167,7 +5166,7 @@
       <c r="L4" s="8"/>
       <c r="M4" s="5"/>
     </row>
-    <row r="5" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A5" s="13">
         <v>4</v>
       </c>
@@ -5188,7 +5187,7 @@
       <c r="L5" s="9"/>
       <c r="M5" s="5"/>
     </row>
-    <row r="6" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
         <v>5</v>
       </c>
@@ -5209,7 +5208,7 @@
       </c>
       <c r="M6" s="5"/>
     </row>
-    <row r="7" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
         <v>6</v>
       </c>
@@ -5230,7 +5229,7 @@
       <c r="L7" s="8"/>
       <c r="M7" s="5"/>
     </row>
-    <row r="8" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
         <v>7</v>
       </c>
@@ -5251,7 +5250,7 @@
       <c r="L8" s="8"/>
       <c r="M8" s="5"/>
     </row>
-    <row r="9" spans="1:13" ht="39.6" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
         <v>8</v>
       </c>
@@ -5274,7 +5273,7 @@
       <c r="L9" s="8"/>
       <c r="M9" s="5"/>
     </row>
-    <row r="10" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
         <v>9</v>
       </c>
@@ -5295,7 +5294,7 @@
       <c r="L10" s="8"/>
       <c r="M10" s="5"/>
     </row>
-    <row r="11" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
         <v>10</v>
       </c>
@@ -5316,7 +5315,7 @@
       <c r="L11" s="8"/>
       <c r="M11" s="5"/>
     </row>
-    <row r="12" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
         <v>11</v>
       </c>
@@ -5337,7 +5336,7 @@
       <c r="L12" s="8"/>
       <c r="M12" s="5"/>
     </row>
-    <row r="13" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
         <v>12</v>
       </c>
@@ -5358,7 +5357,7 @@
       <c r="L13" s="8"/>
       <c r="M13" s="5"/>
     </row>
-    <row r="14" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
         <v>13</v>
       </c>
@@ -5379,7 +5378,7 @@
       <c r="L14" s="8"/>
       <c r="M14" s="5"/>
     </row>
-    <row r="15" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
         <v>14</v>
       </c>
@@ -5400,7 +5399,7 @@
       <c r="L15" s="8"/>
       <c r="M15" s="5"/>
     </row>
-    <row r="16" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
         <v>15</v>
       </c>
@@ -5423,7 +5422,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A17" s="13">
         <v>16</v>
       </c>
@@ -5444,7 +5443,7 @@
       <c r="L17" s="8"/>
       <c r="M17" s="5"/>
     </row>
-    <row r="18" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
         <v>17</v>
       </c>
@@ -5465,7 +5464,7 @@
       </c>
       <c r="M18" s="5"/>
     </row>
-    <row r="19" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
         <v>18</v>
       </c>
@@ -5486,7 +5485,7 @@
       <c r="L19" s="8"/>
       <c r="M19" s="6"/>
     </row>
-    <row r="20" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
         <v>19</v>
       </c>
@@ -5507,7 +5506,7 @@
       <c r="L20" s="8"/>
       <c r="M20" s="6"/>
     </row>
-    <row r="21" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
         <v>20</v>
       </c>
@@ -5528,7 +5527,7 @@
       <c r="L21" s="8"/>
       <c r="M21" s="6"/>
     </row>
-    <row r="22" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
         <v>21</v>
       </c>
@@ -5549,7 +5548,7 @@
       </c>
       <c r="M22" s="5"/>
     </row>
-    <row r="23" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
         <v>22</v>
       </c>
@@ -5570,7 +5569,7 @@
       </c>
       <c r="M23" s="5"/>
     </row>
-    <row r="24" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
         <v>23</v>
       </c>
@@ -5591,7 +5590,7 @@
       </c>
       <c r="M24" s="5"/>
     </row>
-    <row r="25" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
         <v>24</v>
       </c>
@@ -5614,7 +5613,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
         <v>25</v>
       </c>
@@ -5635,7 +5634,7 @@
       <c r="L26" s="8"/>
       <c r="M26" s="6"/>
     </row>
-    <row r="27" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
         <v>26</v>
       </c>
@@ -5656,7 +5655,7 @@
       <c r="L27" s="8"/>
       <c r="M27" s="6"/>
     </row>
-    <row r="28" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
         <v>27</v>
       </c>
@@ -5677,7 +5676,7 @@
       <c r="L28" s="8"/>
       <c r="M28" s="5"/>
     </row>
-    <row r="29" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A29" s="13">
         <v>28</v>
       </c>
@@ -5698,7 +5697,7 @@
       </c>
       <c r="M29" s="5"/>
     </row>
-    <row r="30" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
         <v>29</v>
       </c>
@@ -5719,7 +5718,7 @@
       </c>
       <c r="M30" s="5"/>
     </row>
-    <row r="31" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
         <v>30</v>
       </c>
@@ -5740,7 +5739,7 @@
       <c r="L31" s="8"/>
       <c r="M31" s="6"/>
     </row>
-    <row r="32" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
         <v>31</v>
       </c>
@@ -5786,7 +5785,7 @@
       <c r="L33" s="8"/>
       <c r="M33" s="5"/>
     </row>
-    <row r="34" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
         <v>33</v>
       </c>
@@ -5807,7 +5806,7 @@
       <c r="L34" s="8"/>
       <c r="M34" s="5"/>
     </row>
-    <row r="35" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A35" s="13">
         <v>34</v>
       </c>
@@ -5828,7 +5827,7 @@
       </c>
       <c r="M35" s="5"/>
     </row>
-    <row r="36" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
         <v>35</v>
       </c>
@@ -5849,7 +5848,7 @@
       <c r="L36" s="8"/>
       <c r="M36" s="5"/>
     </row>
-    <row r="37" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A37" s="13">
         <v>36</v>
       </c>
@@ -5897,7 +5896,7 @@
       <c r="L38" s="8"/>
       <c r="M38" s="5"/>
     </row>
-    <row r="39" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
         <v>38</v>
       </c>
@@ -5918,7 +5917,7 @@
       <c r="L39" s="8"/>
       <c r="M39" s="5"/>
     </row>
-    <row r="40" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
         <v>39</v>
       </c>
@@ -5939,7 +5938,7 @@
       <c r="L40" s="8"/>
       <c r="M40" s="5"/>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="13">
         <v>40</v>
       </c>
@@ -5960,7 +5959,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
         <v>41</v>
       </c>
@@ -5981,7 +5980,7 @@
       <c r="L42" s="8"/>
       <c r="M42" s="5"/>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="13">
         <v>42</v>
       </c>
@@ -6002,7 +6001,7 @@
       </c>
       <c r="M43" s="5"/>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
         <v>43</v>
       </c>
@@ -6048,7 +6047,7 @@
       <c r="L45" s="8"/>
       <c r="M45" s="5"/>
     </row>
-    <row r="46" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
         <v>45</v>
       </c>
@@ -6069,7 +6068,7 @@
       <c r="L46" s="8"/>
       <c r="M46" s="6"/>
     </row>
-    <row r="47" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
         <v>46</v>
       </c>
@@ -6090,7 +6089,7 @@
       <c r="L47" s="8"/>
       <c r="M47" s="5"/>
     </row>
-    <row r="48" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
         <v>47</v>
       </c>
@@ -6136,7 +6135,7 @@
       <c r="L49" s="8"/>
       <c r="M49" s="5"/>
     </row>
-    <row r="50" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A50" s="13">
         <v>49</v>
       </c>
@@ -6157,7 +6156,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
         <v>50</v>
       </c>
@@ -6180,7 +6179,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="13">
         <v>51</v>
       </c>
@@ -6203,7 +6202,7 @@
       <c r="L52" s="8"/>
       <c r="M52" s="5"/>
     </row>
-    <row r="53" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A53" s="13">
         <v>52</v>
       </c>
@@ -6226,7 +6225,7 @@
       <c r="L53" s="8"/>
       <c r="M53" s="5"/>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A54" s="13">
         <v>53</v>
       </c>
@@ -6249,7 +6248,7 @@
       <c r="L54" s="8"/>
       <c r="M54" s="5"/>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="13">
         <v>54</v>
       </c>
@@ -6270,7 +6269,7 @@
       </c>
       <c r="M55" s="6"/>
     </row>
-    <row r="56" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A56" s="13">
         <v>55</v>
       </c>
@@ -6293,7 +6292,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="66" x14ac:dyDescent="0.25">
       <c r="A57" s="13">
         <v>56</v>
       </c>
@@ -6314,7 +6313,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A58" s="13">
         <v>57</v>
       </c>
@@ -6360,7 +6359,7 @@
       </c>
       <c r="M59" s="6"/>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A60" s="13">
         <v>59</v>
       </c>
@@ -6408,7 +6407,7 @@
       <c r="L61" s="8"/>
       <c r="M61" s="5"/>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A62" s="13">
         <v>61</v>
       </c>
@@ -6429,7 +6428,7 @@
       </c>
       <c r="M62" s="5"/>
     </row>
-    <row r="63" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A63" s="13">
         <v>62</v>
       </c>
@@ -6450,7 +6449,7 @@
       </c>
       <c r="M63" s="5"/>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A64" s="13">
         <v>63</v>
       </c>
@@ -6471,7 +6470,7 @@
       <c r="L64" s="8"/>
       <c r="M64" s="5"/>
     </row>
-    <row r="65" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A65" s="13">
         <v>64</v>
       </c>
@@ -6492,7 +6491,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A66" s="13">
         <v>65</v>
       </c>
@@ -6540,7 +6539,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A68" s="13">
         <v>67</v>
       </c>
@@ -6611,7 +6610,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="71" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A71" s="13">
         <v>70</v>
       </c>
@@ -6632,7 +6631,7 @@
       <c r="L71" s="8"/>
       <c r="M71" s="5"/>
     </row>
-    <row r="72" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A72" s="13">
         <v>71</v>
       </c>
@@ -6705,7 +6704,7 @@
       </c>
       <c r="M74" s="5"/>
     </row>
-    <row r="75" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A75" s="13">
         <v>74</v>
       </c>
@@ -6726,7 +6725,7 @@
       <c r="L75" s="8"/>
       <c r="M75" s="6"/>
     </row>
-    <row r="76" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A76" s="13">
         <v>75</v>
       </c>
@@ -6747,7 +6746,7 @@
       </c>
       <c r="M76" s="5"/>
     </row>
-    <row r="77" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A77" s="13">
         <v>76</v>
       </c>
@@ -6768,7 +6767,7 @@
       <c r="L77" s="8"/>
       <c r="M77" s="6"/>
     </row>
-    <row r="78" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A78" s="13">
         <v>77</v>
       </c>
@@ -6835,7 +6834,7 @@
       <c r="L80" s="8"/>
       <c r="M80" s="5"/>
     </row>
-    <row r="81" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A81" s="13">
         <v>80</v>
       </c>
@@ -6856,7 +6855,7 @@
       <c r="L81" s="8"/>
       <c r="M81" s="5"/>
     </row>
-    <row r="82" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A82" s="13">
         <v>81</v>
       </c>
@@ -6877,7 +6876,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A83" s="13">
         <v>82</v>
       </c>
@@ -6900,7 +6899,7 @@
       <c r="L83" s="8"/>
       <c r="M83" s="5"/>
     </row>
-    <row r="84" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A84" s="13">
         <v>83</v>
       </c>
@@ -6921,7 +6920,7 @@
       <c r="L84" s="8"/>
       <c r="M84" s="5"/>
     </row>
-    <row r="85" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A85" s="13">
         <v>84</v>
       </c>
@@ -6942,7 +6941,7 @@
       </c>
       <c r="M85" s="5"/>
     </row>
-    <row r="86" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A86" s="13">
         <v>85</v>
       </c>
@@ -6963,7 +6962,7 @@
       <c r="L86" s="8"/>
       <c r="M86" s="5"/>
     </row>
-    <row r="87" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A87" s="13">
         <v>86</v>
       </c>
@@ -6986,7 +6985,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A88" s="13">
         <v>87</v>
       </c>
@@ -7009,7 +7008,7 @@
       <c r="L88" s="8"/>
       <c r="M88" s="5"/>
     </row>
-    <row r="89" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A89" s="13">
         <v>88</v>
       </c>
@@ -7030,7 +7029,7 @@
       <c r="L89" s="8"/>
       <c r="M89" s="5"/>
     </row>
-    <row r="90" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A90" s="13">
         <v>89</v>
       </c>
@@ -7051,7 +7050,7 @@
       <c r="L90" s="8"/>
       <c r="M90" s="5"/>
     </row>
-    <row r="91" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A91" s="13">
         <v>90</v>
       </c>
@@ -7072,7 +7071,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="92" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A92" s="13">
         <v>91</v>
       </c>
@@ -7093,7 +7092,7 @@
       <c r="L92" s="8"/>
       <c r="M92" s="5"/>
     </row>
-    <row r="93" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A93" s="13">
         <v>92</v>
       </c>
@@ -7112,7 +7111,7 @@
       <c r="L93" s="9"/>
       <c r="M93" s="5"/>
     </row>
-    <row r="94" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A94" s="13">
         <v>93</v>
       </c>
@@ -7135,7 +7134,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="95" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A95" s="13">
         <v>94</v>
       </c>
@@ -7158,7 +7157,7 @@
       <c r="L95" s="8"/>
       <c r="M95" s="5"/>
     </row>
-    <row r="96" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A96" s="13">
         <v>95</v>
       </c>
@@ -7179,7 +7178,7 @@
       <c r="L96" s="8"/>
       <c r="M96" s="6"/>
     </row>
-    <row r="97" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A97" s="13">
         <v>96</v>
       </c>
@@ -7202,7 +7201,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A98" s="13">
         <v>97</v>
       </c>
@@ -7223,7 +7222,7 @@
       <c r="L98" s="8"/>
       <c r="M98" s="5"/>
     </row>
-    <row r="99" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A99" s="13">
         <v>98</v>
       </c>
@@ -7246,7 +7245,7 @@
       <c r="L99" s="8"/>
       <c r="M99" s="5"/>
     </row>
-    <row r="100" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A100" s="13">
         <v>99</v>
       </c>
@@ -7267,7 +7266,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="101" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A101" s="13">
         <v>100</v>
       </c>
@@ -7290,7 +7289,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="102" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A102" s="13">
         <v>101</v>
       </c>
@@ -7313,7 +7312,7 @@
       <c r="L102" s="8"/>
       <c r="M102" s="5"/>
     </row>
-    <row r="103" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A103" s="13">
         <v>102</v>
       </c>
@@ -7336,7 +7335,7 @@
       <c r="L103" s="8"/>
       <c r="M103" s="5"/>
     </row>
-    <row r="104" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A104" s="13">
         <v>103</v>
       </c>
@@ -7359,7 +7358,7 @@
       <c r="L104" s="8"/>
       <c r="M104" s="5"/>
     </row>
-    <row r="105" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A105" s="13">
         <v>104</v>
       </c>
@@ -7380,7 +7379,7 @@
       </c>
       <c r="M105" s="6"/>
     </row>
-    <row r="106" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A106" s="13">
         <v>105</v>
       </c>
@@ -7401,7 +7400,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="107" spans="1:13" ht="66" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="66" x14ac:dyDescent="0.25">
       <c r="A107" s="13">
         <v>106</v>
       </c>
@@ -7422,7 +7421,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="108" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A108" s="13">
         <v>107</v>
       </c>
@@ -7447,7 +7446,7 @@
       </c>
       <c r="M108" s="6"/>
     </row>
-    <row r="109" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A109" s="13">
         <v>108</v>
       </c>
@@ -7470,7 +7469,7 @@
       <c r="L109" s="8"/>
       <c r="M109" s="5"/>
     </row>
-    <row r="110" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A110" s="13">
         <v>109</v>
       </c>
@@ -7495,7 +7494,7 @@
       <c r="L110" s="8"/>
       <c r="M110" s="5"/>
     </row>
-    <row r="111" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A111" s="13">
         <v>110</v>
       </c>
@@ -7516,7 +7515,7 @@
       <c r="L111" s="8"/>
       <c r="M111" s="5"/>
     </row>
-    <row r="112" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A112" s="13">
         <v>111</v>
       </c>
@@ -7537,7 +7536,7 @@
       <c r="L112" s="8"/>
       <c r="M112" s="5"/>
     </row>
-    <row r="113" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A113" s="13">
         <v>112</v>
       </c>
@@ -7558,7 +7557,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A114" s="13">
         <v>113</v>
       </c>
@@ -7579,7 +7578,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="115" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A115" s="13">
         <v>114</v>
       </c>
@@ -7606,7 +7605,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A116" s="13">
         <v>115</v>
       </c>
@@ -7627,7 +7626,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="117" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A117" s="13">
         <v>116</v>
       </c>
@@ -7650,7 +7649,7 @@
       <c r="L117" s="8"/>
       <c r="M117" s="5"/>
     </row>
-    <row r="118" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A118" s="13">
         <v>117</v>
       </c>
@@ -7673,7 +7672,7 @@
       <c r="L118" s="8"/>
       <c r="M118" s="5"/>
     </row>
-    <row r="119" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A119" s="13">
         <v>118</v>
       </c>
@@ -7694,7 +7693,7 @@
       <c r="L119" s="8"/>
       <c r="M119" s="5"/>
     </row>
-    <row r="120" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A120" s="13">
         <v>119</v>
       </c>
@@ -7717,7 +7716,7 @@
       <c r="L120" s="8"/>
       <c r="M120" s="5"/>
     </row>
-    <row r="121" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A121" s="13">
         <v>120</v>
       </c>
@@ -7738,7 +7737,7 @@
       <c r="L121" s="8"/>
       <c r="M121" s="6"/>
     </row>
-    <row r="122" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A122" s="13">
         <v>121</v>
       </c>
@@ -7759,7 +7758,7 @@
       </c>
       <c r="M122" s="5"/>
     </row>
-    <row r="123" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A123" s="13">
         <v>122</v>
       </c>
@@ -7780,7 +7779,7 @@
       <c r="L123" s="8"/>
       <c r="M123" s="6"/>
     </row>
-    <row r="124" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A124" s="13">
         <v>123</v>
       </c>
@@ -7801,7 +7800,7 @@
       <c r="L124" s="8"/>
       <c r="M124" s="5"/>
     </row>
-    <row r="125" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A125" s="13">
         <v>124</v>
       </c>
@@ -7822,7 +7821,7 @@
       <c r="L125" s="8"/>
       <c r="M125" s="5"/>
     </row>
-    <row r="126" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A126" s="13">
         <v>125</v>
       </c>
@@ -7845,7 +7844,7 @@
       <c r="L126" s="8"/>
       <c r="M126" s="5"/>
     </row>
-    <row r="127" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A127" s="13">
         <v>126</v>
       </c>
@@ -7866,7 +7865,7 @@
       <c r="L127" s="8"/>
       <c r="M127" s="5"/>
     </row>
-    <row r="128" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A128" s="13">
         <v>127</v>
       </c>
@@ -7887,7 +7886,7 @@
       <c r="L128" s="8"/>
       <c r="M128" s="5"/>
     </row>
-    <row r="129" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A129" s="13">
         <v>128</v>
       </c>
@@ -7908,7 +7907,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A130" s="13">
         <v>129</v>
       </c>
@@ -7929,7 +7928,7 @@
       </c>
       <c r="M130" s="5"/>
     </row>
-    <row r="131" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A131" s="13">
         <v>130</v>
       </c>
@@ -7952,7 +7951,7 @@
       <c r="L131" s="8"/>
       <c r="M131" s="5"/>
     </row>
-    <row r="132" spans="1:13" ht="26.4" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A132" s="13">
         <v>131</v>
       </c>
@@ -7973,7 +7972,7 @@
       </c>
       <c r="M132" s="5"/>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="13">
         <v>132</v>
       </c>
@@ -7994,7 +7993,7 @@
       </c>
       <c r="M133" s="5"/>
     </row>
-    <row r="134" spans="1:13" ht="39.6" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A134" s="13">
         <v>133</v>
       </c>
@@ -8054,7 +8053,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="52.8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A136" s="13">
         <v>135</v>
       </c>
@@ -8150,13 +8149,7 @@
       <c r="M138" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M138" xr:uid="{00000000-0001-0000-0400-000000000000}">
-    <filterColumn colId="2">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M138" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>

--- a/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
+++ b/normas/Herramientas para revisar UNE-EN 301549-2022.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\accesibilidad\normas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8273440-59F9-473C-9828-84E7599CD3C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26FAFF8B-09B8-4814-8BEE-D91B16C15546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{974282F1-0557-4C69-836B-12F6339D2A22}"/>
   </bookViews>
@@ -371,7 +371,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="782" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="796" uniqueCount="254">
   <si>
     <t>5.2 Activación de características de accesibilidad</t>
   </si>
@@ -1135,6 +1135,9 @@
   </si>
   <si>
     <t>Convertidor de documento a txt</t>
+  </si>
+  <si>
+    <t>Funcionalidad cerrada de la propia app</t>
   </si>
 </sst>
 </file>
@@ -2585,13 +2588,13 @@
       <c r="D47" s="8"/>
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
-      <c r="G47" s="9" t="s">
-        <v>141</v>
-      </c>
+      <c r="G47" s="9"/>
       <c r="H47" s="5"/>
       <c r="I47" s="5"/>
       <c r="J47" s="5"/>
-      <c r="K47" s="8"/>
+      <c r="K47" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="L47" s="5"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
@@ -2651,7 +2654,9 @@
       <c r="H50" s="5"/>
       <c r="I50" s="5"/>
       <c r="J50" s="5"/>
-      <c r="K50" s="9"/>
+      <c r="K50" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="L50" s="5"/>
     </row>
     <row r="51" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
@@ -3410,7 +3415,9 @@
       <c r="I86" s="5"/>
       <c r="J86" s="5"/>
       <c r="K86" s="8"/>
-      <c r="L86" s="5"/>
+      <c r="L86" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="87" spans="1:12" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A87" s="15">
@@ -3448,7 +3455,9 @@
       <c r="I88" s="5"/>
       <c r="J88" s="5"/>
       <c r="K88" s="8"/>
-      <c r="L88" s="5"/>
+      <c r="L88" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="89" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A89" s="15">
@@ -3506,7 +3515,9 @@
       <c r="I91" s="5"/>
       <c r="J91" s="5"/>
       <c r="K91" s="8"/>
-      <c r="L91" s="5"/>
+      <c r="L91" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="92" spans="1:12" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A92" s="15">
@@ -3583,13 +3594,13 @@
       <c r="D95" s="8"/>
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
-      <c r="G95" s="9" t="s">
-        <v>141</v>
-      </c>
+      <c r="G95" s="9"/>
       <c r="H95" s="5"/>
       <c r="I95" s="5"/>
       <c r="J95" s="5"/>
-      <c r="K95" s="8"/>
+      <c r="K95" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="L95" s="5"/>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
@@ -3648,7 +3659,9 @@
       <c r="I98" s="5"/>
       <c r="J98" s="5"/>
       <c r="K98" s="8"/>
-      <c r="L98" s="5"/>
+      <c r="L98" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" s="15">
@@ -3665,7 +3678,9 @@
       <c r="H99" s="5"/>
       <c r="I99" s="5"/>
       <c r="J99" s="5"/>
-      <c r="K99" s="8"/>
+      <c r="K99" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="L99" s="5"/>
     </row>
     <row r="100" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
@@ -3748,7 +3763,9 @@
       <c r="I103" s="5"/>
       <c r="J103" s="5"/>
       <c r="K103" s="8"/>
-      <c r="L103" s="5"/>
+      <c r="L103" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="104" spans="1:12" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A104" s="15">
@@ -3786,7 +3803,9 @@
       <c r="I105" s="5"/>
       <c r="J105" s="5"/>
       <c r="K105" s="8"/>
-      <c r="L105" s="5"/>
+      <c r="L105" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="106" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A106" s="15">
@@ -3894,7 +3913,7 @@
       <c r="K110" s="8"/>
       <c r="L110" s="5"/>
     </row>
-    <row r="111" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A111" s="15">
         <v>110</v>
       </c>
@@ -3910,7 +3929,9 @@
       <c r="I111" s="5"/>
       <c r="J111" s="5"/>
       <c r="K111" s="8"/>
-      <c r="L111" s="5"/>
+      <c r="L111" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="112" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A112" s="15">
@@ -3972,7 +3993,9 @@
       <c r="I114" s="5"/>
       <c r="J114" s="5"/>
       <c r="K114" s="8"/>
-      <c r="L114" s="5"/>
+      <c r="L114" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="115" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A115" s="15">
@@ -4242,7 +4265,9 @@
       <c r="I127" s="5"/>
       <c r="J127" s="5"/>
       <c r="K127" s="8"/>
-      <c r="L127" s="5"/>
+      <c r="L127" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="128" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A128" s="15">
@@ -4256,7 +4281,9 @@
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="9"/>
-      <c r="H128" s="5"/>
+      <c r="H128" s="5" t="s">
+        <v>141</v>
+      </c>
       <c r="I128" s="5"/>
       <c r="J128" s="5"/>
       <c r="K128" s="8"/>
@@ -4318,7 +4345,9 @@
       <c r="I131" s="5"/>
       <c r="J131" s="5"/>
       <c r="K131" s="8"/>
-      <c r="L131" s="5"/>
+      <c r="L131" s="5" t="s">
+        <v>253</v>
+      </c>
     </row>
     <row r="132" spans="1:12" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A132" s="15">
@@ -5025,7 +5054,6 @@
       <c r="L163" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L163" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -5928,14 +5956,14 @@
       <c r="D40" s="8"/>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
-      <c r="G40" s="9" t="s">
-        <v>141</v>
-      </c>
+      <c r="G40" s="9"/>
       <c r="H40" s="5"/>
       <c r="I40" s="5"/>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
-      <c r="L40" s="8"/>
+      <c r="L40" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="M40" s="5"/>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.25">
@@ -7040,14 +7068,14 @@
       <c r="D90" s="8"/>
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
-      <c r="G90" s="9" t="s">
-        <v>141</v>
-      </c>
+      <c r="G90" s="9"/>
       <c r="H90" s="5"/>
       <c r="I90" s="5"/>
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
-      <c r="L90" s="8"/>
+      <c r="L90" s="8" t="s">
+        <v>141</v>
+      </c>
       <c r="M90" s="5"/>
     </row>
     <row r="91" spans="1:13" x14ac:dyDescent="0.25">
@@ -7108,7 +7136,9 @@
       <c r="I93" s="5"/>
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
-      <c r="L93" s="9"/>
+      <c r="L93" s="9" t="s">
+        <v>141</v>
+      </c>
       <c r="M93" s="5"/>
     </row>
     <row r="94" spans="1:13" ht="26.4" x14ac:dyDescent="0.25">
@@ -8149,7 +8179,6 @@
       <c r="M138" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M138" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
